--- a/upload/report/scm_po.xlsx
+++ b/upload/report/scm_po.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="121">
   <si>
     <t>Customer PO No.</t>
   </si>
@@ -119,10 +119,10 @@
     <t>Shipping Method</t>
   </si>
   <si>
-    <t>132528</t>
-  </si>
-  <si>
-    <t>7173LIMA2-S</t>
+    <t>132676</t>
+  </si>
+  <si>
+    <t>815VS-S</t>
   </si>
   <si>
     <t>PEN</t>
@@ -131,73 +131,253 @@
     <t>20240327</t>
   </si>
   <si>
-    <t>REFRIGERADORA LG - GT26BPP</t>
-  </si>
-  <si>
-    <t>124</t>
+    <t>GB46TGT.AMCGLPR</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>3056.8800</t>
+  </si>
+  <si>
+    <t>20240312</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES HIRAOKA S.A.C.</t>
+  </si>
+  <si>
+    <t>GT24BPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>1229.7600</t>
+  </si>
+  <si>
+    <t>GT31WPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>1453.4900</t>
+  </si>
+  <si>
+    <t>GT33BPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>1490.7800</t>
+  </si>
+  <si>
+    <t>GT37SGP.APZGLPR</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>1677.2200</t>
+  </si>
+  <si>
+    <t>GT39SGP1.APZGLPR</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>2087.3900</t>
+  </si>
+  <si>
+    <t>GT51SGD.ABLGLPR</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>2758.5800</t>
+  </si>
+  <si>
+    <t>GT57BPSX.ASTGLPR</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>2684.0000</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>5319.6100</t>
+  </si>
+  <si>
+    <t>GS51MPD.AHBGLPR</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>2012.8100</t>
+  </si>
+  <si>
+    <t>LS66SPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>3877.2200</t>
+  </si>
+  <si>
+    <t>LS66SDP.APZGLPR</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>4250.1000</t>
+  </si>
+  <si>
+    <t>LS66SXT.AMCGLPR</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>6194.1900</t>
+  </si>
+  <si>
+    <t>WD11PVC3S6.APTGLGP</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>1714.5100</t>
+  </si>
+  <si>
+    <t>WD15BG2S.ABLGLGP</t>
+  </si>
+  <si>
+    <t>2477.2400</t>
+  </si>
+  <si>
+    <t>WD20VV2S6R.ASSGLGP</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>3416.2400</t>
+  </si>
+  <si>
+    <t>WK14BS6.APBGLGP</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>5551.8300</t>
+  </si>
+  <si>
+    <t>WK22BS6.ABLGLGP</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>6406.0700</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>WT16BPB.ABMGLGP</t>
+  </si>
+  <si>
+    <t>164</t>
   </si>
   <si>
     <t>1304.3400</t>
   </si>
   <si>
-    <t>20240305</t>
-  </si>
-  <si>
-    <t>EH INVERSIONES S.A.C.</t>
-  </si>
-  <si>
-    <t>REFRIGERADORA LG - LS66SPG</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>3429.7600</t>
-  </si>
-  <si>
-    <t>LAVADORA SECADORA LG - WD9PVC4S6</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1565.3600</t>
-  </si>
-  <si>
-    <t>REFRIGERADORA LG - GT31BPP</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>1416.2000</t>
-  </si>
-  <si>
-    <t>REFRIGERADORA LG - GB37WGT</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>2236.5400</t>
-  </si>
-  <si>
-    <t>LAVADORA LG - WM10WVC4S6</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>1490.7800</t>
-  </si>
-  <si>
-    <t>REFRIGERADORA LG - LS51BPP</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>1938.2400</t>
+    <t>WT23PBVS6.APBGLGP</t>
+  </si>
+  <si>
+    <t>2404.3600</t>
+  </si>
+  <si>
+    <t>WT25PBVS6.APBGLGP</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>2550.1200</t>
+  </si>
+  <si>
+    <t>LRGL5845S.BSTGLPR</t>
+  </si>
+  <si>
+    <t>3629.8000</t>
+  </si>
+  <si>
+    <t>LRGL5847S.BSTGLPR</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3985.7300</t>
+  </si>
+  <si>
+    <t>LRGZ5253S.CSTGLPR</t>
+  </si>
+  <si>
+    <t>1423.0200</t>
+  </si>
+  <si>
+    <t>LRGZ5255S.CSTGLPR</t>
+  </si>
+  <si>
+    <t>1494.2000</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>363.6800</t>
+  </si>
+  <si>
+    <t>MH7032JAS.BBKGLPR</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>349.1000</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>509.4400</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>327.2400</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>436.5600</t>
   </si>
 </sst>
 </file>
@@ -537,7 +717,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AH33"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -1021,6 +1201,1342 @@
       <c r="AF8"/>
       <c r="AG8"/>
       <c r="AH8"/>
+    </row>
+    <row r="9" spans="1:34">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
+      <c r="AE9"/>
+      <c r="AF9"/>
+      <c r="AG9"/>
+      <c r="AH9"/>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10"/>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10"/>
+      <c r="AG10"/>
+      <c r="AH10"/>
+    </row>
+    <row r="11" spans="1:34">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
+      <c r="AE11"/>
+      <c r="AF11"/>
+      <c r="AG11"/>
+      <c r="AH11"/>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA12"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12"/>
+      <c r="AE12"/>
+      <c r="AF12"/>
+      <c r="AG12"/>
+      <c r="AH12"/>
+    </row>
+    <row r="13" spans="1:34">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13" t="s">
+        <v>41</v>
+      </c>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="Z13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA13"/>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
+      <c r="AE13"/>
+      <c r="AF13"/>
+      <c r="AG13"/>
+      <c r="AH13"/>
+    </row>
+    <row r="14" spans="1:34">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14" t="s">
+        <v>41</v>
+      </c>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA14"/>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
+      <c r="AE14"/>
+      <c r="AF14"/>
+      <c r="AG14"/>
+      <c r="AH14"/>
+    </row>
+    <row r="15" spans="1:34">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA15"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15"/>
+      <c r="AF15"/>
+      <c r="AG15"/>
+      <c r="AH15"/>
+    </row>
+    <row r="16" spans="1:34">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16" t="s">
+        <v>41</v>
+      </c>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16"/>
+      <c r="AG16"/>
+      <c r="AH16"/>
+    </row>
+    <row r="17" spans="1:34">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17" t="s">
+        <v>41</v>
+      </c>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17"/>
+      <c r="Z17" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA17"/>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
+      <c r="AE17"/>
+      <c r="AF17"/>
+      <c r="AG17"/>
+      <c r="AH17"/>
+    </row>
+    <row r="18" spans="1:34">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18" t="s">
+        <v>41</v>
+      </c>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA18"/>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
+      <c r="AE18"/>
+      <c r="AF18"/>
+      <c r="AG18"/>
+      <c r="AH18"/>
+    </row>
+    <row r="19" spans="1:34">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA19"/>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19"/>
+      <c r="AF19"/>
+      <c r="AG19"/>
+      <c r="AH19"/>
+    </row>
+    <row r="20" spans="1:34">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20"/>
+      <c r="F20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20" t="s">
+        <v>41</v>
+      </c>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
+      <c r="Y20"/>
+      <c r="Z20" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA20"/>
+      <c r="AB20"/>
+      <c r="AC20"/>
+      <c r="AD20"/>
+      <c r="AE20"/>
+      <c r="AF20"/>
+      <c r="AG20"/>
+      <c r="AH20"/>
+    </row>
+    <row r="21" spans="1:34">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+      <c r="Y21"/>
+      <c r="Z21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA21"/>
+      <c r="AB21"/>
+      <c r="AC21"/>
+      <c r="AD21"/>
+      <c r="AE21"/>
+      <c r="AF21"/>
+      <c r="AG21"/>
+      <c r="AH21"/>
+    </row>
+    <row r="22" spans="1:34">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22" t="s">
+        <v>41</v>
+      </c>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22"/>
+      <c r="AF22"/>
+      <c r="AG22"/>
+      <c r="AH22"/>
+    </row>
+    <row r="23" spans="1:34">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23"/>
+      <c r="Z23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA23"/>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
+      <c r="AE23"/>
+      <c r="AF23"/>
+      <c r="AG23"/>
+      <c r="AH23"/>
+    </row>
+    <row r="24" spans="1:34">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24" t="s">
+        <v>41</v>
+      </c>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+      <c r="S24"/>
+      <c r="T24"/>
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+      <c r="Y24"/>
+      <c r="Z24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA24"/>
+      <c r="AB24"/>
+      <c r="AC24"/>
+      <c r="AD24"/>
+      <c r="AE24"/>
+      <c r="AF24"/>
+      <c r="AG24"/>
+      <c r="AH24"/>
+    </row>
+    <row r="25" spans="1:34">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" t="s">
+        <v>105</v>
+      </c>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25" t="s">
+        <v>41</v>
+      </c>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+      <c r="S25"/>
+      <c r="T25"/>
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="Y25"/>
+      <c r="Z25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA25"/>
+      <c r="AB25"/>
+      <c r="AC25"/>
+      <c r="AD25"/>
+      <c r="AE25"/>
+      <c r="AF25"/>
+      <c r="AG25"/>
+      <c r="AH25"/>
+    </row>
+    <row r="26" spans="1:34">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26" t="s">
+        <v>41</v>
+      </c>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+      <c r="Y26"/>
+      <c r="Z26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA26"/>
+      <c r="AB26"/>
+      <c r="AC26"/>
+      <c r="AD26"/>
+      <c r="AE26"/>
+      <c r="AF26"/>
+      <c r="AG26"/>
+      <c r="AH26"/>
+    </row>
+    <row r="27" spans="1:34">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27" t="s">
+        <v>41</v>
+      </c>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+      <c r="Y27"/>
+      <c r="Z27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA27"/>
+      <c r="AB27"/>
+      <c r="AC27"/>
+      <c r="AD27"/>
+      <c r="AE27"/>
+      <c r="AF27"/>
+      <c r="AG27"/>
+      <c r="AH27"/>
+    </row>
+    <row r="28" spans="1:34">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28"/>
+      <c r="F28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" t="s">
+        <v>111</v>
+      </c>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28" t="s">
+        <v>41</v>
+      </c>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+      <c r="S28"/>
+      <c r="T28"/>
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+      <c r="Y28"/>
+      <c r="Z28" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA28"/>
+      <c r="AB28"/>
+      <c r="AC28"/>
+      <c r="AD28"/>
+      <c r="AE28"/>
+      <c r="AF28"/>
+      <c r="AG28"/>
+      <c r="AH28"/>
+    </row>
+    <row r="29" spans="1:34">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29" t="s">
+        <v>114</v>
+      </c>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29" t="s">
+        <v>41</v>
+      </c>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+      <c r="S29"/>
+      <c r="T29"/>
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+      <c r="Y29"/>
+      <c r="Z29" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA29"/>
+      <c r="AB29"/>
+      <c r="AC29"/>
+      <c r="AD29"/>
+      <c r="AE29"/>
+      <c r="AF29"/>
+      <c r="AG29"/>
+      <c r="AH29"/>
+    </row>
+    <row r="30" spans="1:34">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30"/>
+      <c r="F30" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30" t="s">
+        <v>41</v>
+      </c>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+      <c r="S30"/>
+      <c r="T30"/>
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA30"/>
+      <c r="AB30"/>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30"/>
+      <c r="AF30"/>
+      <c r="AG30"/>
+      <c r="AH30"/>
+    </row>
+    <row r="31" spans="1:34">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31"/>
+      <c r="F31" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31" t="s">
+        <v>41</v>
+      </c>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+      <c r="S31"/>
+      <c r="T31"/>
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="Y31"/>
+      <c r="Z31" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA31"/>
+      <c r="AB31"/>
+      <c r="AC31"/>
+      <c r="AD31"/>
+      <c r="AE31"/>
+      <c r="AF31"/>
+      <c r="AG31"/>
+      <c r="AH31"/>
+    </row>
+    <row r="32" spans="1:34">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32"/>
+      <c r="F32" t="s">
+        <v>119</v>
+      </c>
+      <c r="G32" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32" t="s">
+        <v>41</v>
+      </c>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+      <c r="S32"/>
+      <c r="T32"/>
+      <c r="U32"/>
+      <c r="V32"/>
+      <c r="W32"/>
+      <c r="X32"/>
+      <c r="Y32"/>
+      <c r="Z32" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA32"/>
+      <c r="AB32"/>
+      <c r="AC32"/>
+      <c r="AD32"/>
+      <c r="AE32"/>
+      <c r="AF32"/>
+      <c r="AG32"/>
+      <c r="AH32"/>
+    </row>
+    <row r="33" spans="1:34">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33"/>
+      <c r="F33" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" t="s">
+        <v>120</v>
+      </c>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33" t="s">
+        <v>41</v>
+      </c>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+      <c r="S33"/>
+      <c r="T33"/>
+      <c r="U33"/>
+      <c r="V33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+      <c r="Y33"/>
+      <c r="Z33" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA33"/>
+      <c r="AB33"/>
+      <c r="AC33"/>
+      <c r="AD33"/>
+      <c r="AE33"/>
+      <c r="AF33"/>
+      <c r="AG33"/>
+      <c r="AH33"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>

--- a/upload/report/scm_po.xlsx
+++ b/upload/report/scm_po.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="71">
   <si>
     <t>Customer PO No.</t>
   </si>
@@ -119,85 +119,115 @@
     <t>Shipping Method</t>
   </si>
   <si>
-    <t>132668</t>
-  </si>
-  <si>
-    <t>815VS-S</t>
+    <t>4800052222</t>
+  </si>
+  <si>
+    <t>8104VILLA-S</t>
   </si>
   <si>
     <t>PEN</t>
   </si>
   <si>
+    <t>20240606</t>
+  </si>
+  <si>
+    <t>No SKU: GS51MPD</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>1931.53</t>
+  </si>
+  <si>
     <t>20240327</t>
   </si>
   <si>
-    <t>20.0000</t>
-  </si>
-  <si>
-    <t>800.9700</t>
-  </si>
-  <si>
-    <t>20240312</t>
-  </si>
-  <si>
-    <t>IMPORTACIONES HIRAOKA S.A.C.</t>
-  </si>
-  <si>
-    <t>RNC9.DPERLLK</t>
-  </si>
-  <si>
-    <t>25.0000</t>
-  </si>
-  <si>
-    <t>1041.6800</t>
-  </si>
-  <si>
-    <t>XG5QBK.DPERLLK</t>
-  </si>
-  <si>
-    <t>10.0000</t>
-  </si>
-  <si>
-    <t>266.3600</t>
-  </si>
-  <si>
-    <t>XG5QGR.DPERLLK</t>
-  </si>
-  <si>
-    <t>4.0000</t>
-  </si>
-  <si>
-    <t>XG7QBK.DPERLLK</t>
-  </si>
-  <si>
-    <t>35.0000</t>
-  </si>
-  <si>
-    <t>414.6600</t>
-  </si>
-  <si>
-    <t>S75Q.DPERLLK</t>
-  </si>
-  <si>
-    <t>17.0000</t>
-  </si>
-  <si>
-    <t>1416.2000</t>
-  </si>
-  <si>
-    <t>SQC1.DPERLLK</t>
-  </si>
-  <si>
-    <t>446.7100</t>
-  </si>
-  <si>
-    <t>CK43N.DPERLLK</t>
-  </si>
-  <si>
-    <t>14.0000</t>
-  </si>
-  <si>
-    <t>436.5600</t>
+    <t>CONECTA RETAIL SELVA S.A.C.</t>
+  </si>
+  <si>
+    <t>No SKU: GT51SGD</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2609.49</t>
+  </si>
+  <si>
+    <t>No SKU: LM57SPN</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4097.64</t>
+  </si>
+  <si>
+    <t>No SKU: LRGL5845S</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3436.63</t>
+  </si>
+  <si>
+    <t>No SKU: LRGZ5255S</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>1453.58</t>
+  </si>
+  <si>
+    <t>No SKU: MH6596DIR</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>395.41</t>
+  </si>
+  <si>
+    <t>No SKU: MH7032JAS</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>346.76</t>
+  </si>
+  <si>
+    <t>No SKU: MH8296DIR</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>499.64</t>
+  </si>
+  <si>
+    <t>No SKU: MS2536GIS</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>325.92</t>
+  </si>
+  <si>
+    <t>No SKU: MS2596DIR</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>No SKU: MS4296DIR</t>
+  </si>
+  <si>
+    <t>430.15</t>
   </si>
 </sst>
 </file>
@@ -537,7 +567,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -657,12 +687,14 @@
       <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="E2"/>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
@@ -670,7 +702,7 @@
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2"/>
       <c r="O2"/>
@@ -685,7 +717,7 @@
       <c r="X2"/>
       <c r="Y2"/>
       <c r="Z2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA2"/>
       <c r="AB2"/>
@@ -710,13 +742,13 @@
         <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -724,7 +756,7 @@
       <c r="K3"/>
       <c r="L3"/>
       <c r="M3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N3"/>
       <c r="O3"/>
@@ -739,7 +771,7 @@
       <c r="X3"/>
       <c r="Y3"/>
       <c r="Z3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA3"/>
       <c r="AB3"/>
@@ -764,13 +796,13 @@
         <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
@@ -778,7 +810,7 @@
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N4"/>
       <c r="O4"/>
@@ -793,7 +825,7 @@
       <c r="X4"/>
       <c r="Y4"/>
       <c r="Z4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA4"/>
       <c r="AB4"/>
@@ -818,13 +850,13 @@
         <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
@@ -832,7 +864,7 @@
       <c r="K5"/>
       <c r="L5"/>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N5"/>
       <c r="O5"/>
@@ -847,7 +879,7 @@
       <c r="X5"/>
       <c r="Y5"/>
       <c r="Z5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA5"/>
       <c r="AB5"/>
@@ -872,13 +904,13 @@
         <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
@@ -886,7 +918,7 @@
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N6"/>
       <c r="O6"/>
@@ -901,7 +933,7 @@
       <c r="X6"/>
       <c r="Y6"/>
       <c r="Z6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA6"/>
       <c r="AB6"/>
@@ -926,13 +958,13 @@
         <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
@@ -940,7 +972,7 @@
       <c r="K7"/>
       <c r="L7"/>
       <c r="M7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N7"/>
       <c r="O7"/>
@@ -955,7 +987,7 @@
       <c r="X7"/>
       <c r="Y7"/>
       <c r="Z7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA7"/>
       <c r="AB7"/>
@@ -980,13 +1012,13 @@
         <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
@@ -994,7 +1026,7 @@
       <c r="K8"/>
       <c r="L8"/>
       <c r="M8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N8"/>
       <c r="O8"/>
@@ -1009,7 +1041,7 @@
       <c r="X8"/>
       <c r="Y8"/>
       <c r="Z8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA8"/>
       <c r="AB8"/>
@@ -1034,13 +1066,13 @@
         <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
@@ -1048,7 +1080,7 @@
       <c r="K9"/>
       <c r="L9"/>
       <c r="M9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N9"/>
       <c r="O9"/>
@@ -1063,7 +1095,7 @@
       <c r="X9"/>
       <c r="Y9"/>
       <c r="Z9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA9"/>
       <c r="AB9"/>
@@ -1073,6 +1105,168 @@
       <c r="AF9"/>
       <c r="AG9"/>
       <c r="AH9"/>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10"/>
+      <c r="AG10"/>
+      <c r="AH10"/>
+    </row>
+    <row r="11" spans="1:34">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
+      <c r="AE11"/>
+      <c r="AF11"/>
+      <c r="AG11"/>
+      <c r="AH11"/>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA12"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12"/>
+      <c r="AE12"/>
+      <c r="AF12"/>
+      <c r="AG12"/>
+      <c r="AH12"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
